--- a/data/scuc-xmr-charts-2016-2022.xlsx
+++ b/data/scuc-xmr-charts-2016-2022.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/D/Library/Mobile Documents/com~apple~CloudDocs/R Working Directory/scuc-data-analysis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/D/Library/Mobile Documents/com~apple~CloudDocs/R Working Directory/scuc-data-analysis/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89B1F792-05D4-8E4D-8000-E0B39E29E176}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{19DA11AE-764E-AB44-A70A-41885D587A08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="32000" windowHeight="17500" activeTab="2" xr2:uid="{E446ED3B-4AEC-8C41-8BB6-324FD235385F}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="32000" windowHeight="17500" xr2:uid="{E446ED3B-4AEC-8C41-8BB6-324FD235385F}"/>
   </bookViews>
   <sheets>
     <sheet name="2016-2022 XmR all sub apponly" sheetId="17" r:id="rId1"/>
